--- a/مرجع-الطبخات.xlsx
+++ b/مرجع-الطبخات.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE6E1C39-147A-40C1-9844-D2B0812F1EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6694CCEE-B145-4223-9193-2EDE68CECCAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="656" firstSheet="40" activeTab="42" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="656" firstSheet="36" activeTab="36" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="لودلين سادة أول" sheetId="9" r:id="rId1"/>
@@ -49,15 +49,17 @@
     <sheet name="طبخة قاشط" sheetId="4" r:id="rId34"/>
     <sheet name="دوا غسيل بودرا 60 كغ -عطر ببوري" sheetId="49" r:id="rId35"/>
     <sheet name="دوا غسيل بودرا 157 كغ - ببوري" sheetId="50" r:id="rId36"/>
-    <sheet name="دوا غسيل بودرا 45كغ مصنع" sheetId="52" r:id="rId37"/>
-    <sheet name="طبخة دوا غسيل بودرا" sheetId="3" r:id="rId38"/>
-    <sheet name="طبخة الشامبو" sheetId="1" r:id="rId39"/>
-    <sheet name="صابون سائل ماء الذهب" sheetId="44" r:id="rId40"/>
-    <sheet name="صابون سائل عود" sheetId="45" r:id="rId41"/>
-    <sheet name="صابون سائل رمان - لافندر" sheetId="51" r:id="rId42"/>
-    <sheet name="صابون سادة" sheetId="2" r:id="rId43"/>
-    <sheet name="جدول فارغ غير قابل للتعديل" sheetId="10" r:id="rId44"/>
-    <sheet name="طبخة جديدة 2 (3)" sheetId="14" r:id="rId45"/>
+    <sheet name="دوا غسيل بودرا - اندومي 100 كغ" sheetId="55" r:id="rId37"/>
+    <sheet name="دوا غسيل بودرا 45كغ مصنع" sheetId="52" r:id="rId38"/>
+    <sheet name="طبخة دوا غسيل بودرا" sheetId="3" r:id="rId39"/>
+    <sheet name="طبخة الشامبو" sheetId="1" r:id="rId40"/>
+    <sheet name="صابون سائل ماء الذهب" sheetId="44" r:id="rId41"/>
+    <sheet name="صابون سائل عود" sheetId="45" r:id="rId42"/>
+    <sheet name="صابون سائل رمان - لافندر" sheetId="51" r:id="rId43"/>
+    <sheet name="صابون سادة" sheetId="2" r:id="rId44"/>
+    <sheet name="طبخة ابو رفيق مغاسل 1.5 طون" sheetId="53" r:id="rId45"/>
+    <sheet name="جدول فارغ غير قابل للتعديل" sheetId="10" r:id="rId46"/>
+    <sheet name="طبخة جديدة 2 (3)" sheetId="14" r:id="rId47"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -75,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="95">
   <si>
     <t>رقم</t>
   </si>
@@ -358,6 +360,9 @@
   <si>
     <t>ديباتيول فينب (5)</t>
   </si>
+  <si>
+    <t>فورمول سم</t>
+  </si>
 </sst>
 </file>
 
@@ -550,7 +555,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -601,11 +606,12 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -621,13 +627,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
@@ -1099,12 +1103,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="27"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="4"/>
@@ -1363,12 +1367,12 @@
     </row>
     <row r="12" spans="1:6" ht="21" customHeight="1">
       <c r="A12" s="5"/>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="27"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:6" ht="16.5">
       <c r="A13" s="4"/>
@@ -1637,12 +1641,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="27"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
@@ -1906,12 +1910,12 @@
     </row>
     <row r="13" spans="1:5" ht="21" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="27"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
@@ -2176,12 +2180,12 @@
     </row>
     <row r="13" spans="1:5" ht="18.75" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="30"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -2430,12 +2434,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="27"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="4"/>
@@ -2706,12 +2710,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="27"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="14"/>
@@ -2976,12 +2980,12 @@
     </row>
     <row r="13" spans="1:5" ht="21" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="30"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -3245,12 +3249,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="33"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -3504,12 +3508,12 @@
     </row>
     <row r="12" spans="1:5" ht="23.25" customHeight="1">
       <c r="A12" s="5"/>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="27"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="4"/>
@@ -3778,12 +3782,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="27"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
@@ -4014,12 +4018,12 @@
     </row>
     <row r="12" spans="1:5" ht="23.25" customHeight="1">
       <c r="A12" s="9"/>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="30"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="10"/>
@@ -4235,12 +4239,12 @@
     </row>
     <row r="13" spans="1:5" ht="23.25" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="27"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
@@ -4505,12 +4509,12 @@
     </row>
     <row r="13" spans="1:5" ht="27" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="30"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -4702,12 +4706,12 @@
     </row>
     <row r="8" spans="1:5" ht="27.75" customHeight="1">
       <c r="A8" s="5"/>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="27"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -4923,12 +4927,12 @@
     </row>
     <row r="8" spans="1:5" ht="16.5">
       <c r="A8" s="5"/>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="27"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -5144,12 +5148,12 @@
     </row>
     <row r="8" spans="1:5" ht="16.5">
       <c r="A8" s="9"/>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="30"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="13"/>
@@ -5376,12 +5380,12 @@
     </row>
     <row r="8" spans="1:5" ht="32.25" customHeight="1">
       <c r="A8" s="5"/>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="27"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -5608,12 +5612,12 @@
     </row>
     <row r="8" spans="1:5" ht="30" customHeight="1">
       <c r="A8" s="5"/>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="27"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -5843,12 +5847,12 @@
     </row>
     <row r="8" spans="1:5" ht="31.5" customHeight="1">
       <c r="A8" s="5"/>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="27"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -6064,12 +6068,12 @@
     </row>
     <row r="8" spans="1:5" ht="16.5">
       <c r="A8" s="5"/>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="27"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -6290,12 +6294,12 @@
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="5"/>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="27"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6481,12 +6485,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="27"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="14"/>
@@ -6764,12 +6768,12 @@
     </row>
     <row r="22" spans="1:5" ht="16.5">
       <c r="A22" s="5"/>
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="27"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6941,12 +6945,12 @@
     </row>
     <row r="11" spans="1:5" ht="16.5">
       <c r="A11" s="5"/>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="27"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="4"/>
@@ -7245,12 +7249,12 @@
     </row>
     <row r="11" spans="1:5" ht="16.5">
       <c r="A11" s="5"/>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="27"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="4"/>
@@ -7549,12 +7553,12 @@
     </row>
     <row r="11" spans="1:5" ht="16.5">
       <c r="A11" s="5"/>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="27"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="4"/>
@@ -7908,12 +7912,12 @@
     </row>
     <row r="25" spans="1:5" ht="16.5">
       <c r="A25" s="5"/>
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="27"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8043,12 +8047,12 @@
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="5"/>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="27"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26"/>
     </row>
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="4"/>
@@ -8299,12 +8303,12 @@
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="5"/>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="27"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26"/>
     </row>
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="4"/>
@@ -8436,6 +8440,245 @@
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEC35E0-DAF5-4502-B6DD-6FD4EB7D4329}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="20.25" customHeight="1">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="2">
+        <v>60</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5" ht="20.25" customHeight="1">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="2">
+        <v>35</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="2">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" ht="20.25" customHeight="1">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2">
+        <v>200</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5" ht="16.5">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" ht="16.5">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" ht="16.5">
+      <c r="A8" s="5"/>
+      <c r="B8" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
+    </row>
+    <row r="9" spans="1:5" ht="16.5">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" ht="16.5">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" ht="16.5">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" ht="16.5">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" ht="16.5">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" ht="16.5">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" ht="16.5">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" ht="16.5">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" ht="16.5">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" ht="16.5">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" ht="16.5">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" ht="16.5">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" ht="16.5">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:5" ht="16.5">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5" ht="16.5">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:5" ht="16.5">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5" ht="16.5">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B8:E8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B495554-5330-4E3B-92F2-BCD610347704}">
   <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -8555,12 +8798,12 @@
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="5"/>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="27"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26"/>
     </row>
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="4"/>
@@ -8689,7 +8932,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:E26"/>
@@ -8810,12 +9053,12 @@
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="5"/>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="27"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26"/>
     </row>
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="4"/>
@@ -8943,369 +9186,6 @@
     <mergeCell ref="B9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet25">
-    <tabColor theme="1" tint="0.499984740745262"/>
-  </sheetPr>
-  <dimension ref="A1:E33"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="20.25" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="60.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="19" customFormat="1" ht="27">
-      <c r="A2" s="17">
-        <v>1</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="17">
-        <v>140</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="18"/>
-    </row>
-    <row r="3" spans="1:5" s="19" customFormat="1" ht="27">
-      <c r="A3" s="17">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="17">
-        <v>30</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="18"/>
-    </row>
-    <row r="4" spans="1:5" s="19" customFormat="1" ht="27">
-      <c r="A4" s="17">
-        <v>3</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="17">
-        <v>50</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="18"/>
-    </row>
-    <row r="5" spans="1:5" s="19" customFormat="1" ht="27">
-      <c r="A5" s="17">
-        <v>4</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="17">
-        <v>10</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" s="19" customFormat="1" ht="27">
-      <c r="A6" s="17">
-        <v>5</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="17">
-        <v>12.5</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" s="19" customFormat="1" ht="27">
-      <c r="A7" s="17">
-        <v>6</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="17">
-        <v>950</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="18"/>
-    </row>
-    <row r="8" spans="1:5" s="19" customFormat="1" ht="27">
-      <c r="A8" s="17">
-        <v>7</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" s="17">
-        <v>500</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="18"/>
-    </row>
-    <row r="9" spans="1:5" s="19" customFormat="1" ht="27">
-      <c r="A9" s="17">
-        <v>8</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="17">
-        <v>1</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="18"/>
-    </row>
-    <row r="10" spans="1:5" s="19" customFormat="1" ht="27">
-      <c r="A10" s="17">
-        <v>9</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="17">
-        <v>5</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="18"/>
-    </row>
-    <row r="11" spans="1:5" s="19" customFormat="1" ht="27">
-      <c r="A11" s="17">
-        <v>10</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="18"/>
-    </row>
-    <row r="12" spans="1:5" s="19" customFormat="1" ht="27">
-      <c r="A12" s="17">
-        <v>11</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="17">
-        <v>3</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="18"/>
-    </row>
-    <row r="13" spans="1:5" s="19" customFormat="1" ht="27">
-      <c r="A13" s="17">
-        <v>12</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="17">
-        <v>750</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="18"/>
-    </row>
-    <row r="14" spans="1:5" s="19" customFormat="1" ht="27">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-    </row>
-    <row r="15" spans="1:5" s="19" customFormat="1" ht="27">
-      <c r="A15" s="20"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-    </row>
-    <row r="16" spans="1:5" s="19" customFormat="1" ht="27">
-      <c r="A16" s="20"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-    </row>
-    <row r="17" spans="1:5" s="19" customFormat="1" ht="27">
-      <c r="A17" s="20"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-    </row>
-    <row r="18" spans="1:5" s="19" customFormat="1" ht="27">
-      <c r="A18" s="20"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-    </row>
-    <row r="19" spans="1:5" s="19" customFormat="1" ht="27.75">
-      <c r="A19" s="21"/>
-      <c r="B19" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="24"/>
-    </row>
-    <row r="20" spans="1:5" ht="16.5">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-    </row>
-    <row r="21" spans="1:5" ht="16.5">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-    </row>
-    <row r="22" spans="1:5" ht="16.5">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-    </row>
-    <row r="23" spans="1:5" ht="16.5">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-    </row>
-    <row r="24" spans="1:5" ht="16.5">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-    </row>
-    <row r="25" spans="1:5" ht="16.5">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-    </row>
-    <row r="26" spans="1:5" ht="16.5">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-    </row>
-    <row r="27" spans="1:5" ht="16.5">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-    </row>
-    <row r="28" spans="1:5" ht="16.5">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-    </row>
-    <row r="29" spans="1:5" ht="16.5">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-    </row>
-    <row r="30" spans="1:5" ht="16.5">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-    </row>
-    <row r="31" spans="1:5" ht="16.5">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-    </row>
-    <row r="32" spans="1:5" ht="16.5">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-    </row>
-    <row r="33" spans="1:5" ht="16.5">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B19:E19"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.34" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9483,12 +9363,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="27"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="4"/>
@@ -9562,6 +9442,369 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet25">
+    <tabColor theme="1" tint="0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="20.25" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="60.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A2" s="17">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="17">
+        <v>140</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="18"/>
+    </row>
+    <row r="3" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="17">
+        <v>30</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="18"/>
+    </row>
+    <row r="4" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A4" s="17">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="17">
+        <v>50</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="18"/>
+    </row>
+    <row r="5" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A5" s="17">
+        <v>4</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="17">
+        <v>10</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="18"/>
+    </row>
+    <row r="6" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A6" s="17">
+        <v>5</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="17">
+        <v>12.5</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="18"/>
+    </row>
+    <row r="7" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A7" s="17">
+        <v>6</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="17">
+        <v>950</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="18"/>
+    </row>
+    <row r="8" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A8" s="17">
+        <v>7</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="17">
+        <v>500</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="18"/>
+    </row>
+    <row r="9" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A9" s="17">
+        <v>8</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="17">
+        <v>1</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="18"/>
+    </row>
+    <row r="10" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A10" s="17">
+        <v>9</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="17">
+        <v>5</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="18"/>
+    </row>
+    <row r="11" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A11" s="17">
+        <v>10</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="18"/>
+    </row>
+    <row r="12" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A12" s="17">
+        <v>11</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="17">
+        <v>3</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="18"/>
+    </row>
+    <row r="13" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A13" s="17">
+        <v>12</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="17">
+        <v>750</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="18"/>
+    </row>
+    <row r="14" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+    </row>
+    <row r="15" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+    </row>
+    <row r="16" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+    </row>
+    <row r="17" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+    </row>
+    <row r="18" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+    </row>
+    <row r="19" spans="1:5" s="19" customFormat="1" ht="27.75">
+      <c r="A19" s="21"/>
+      <c r="B19" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="35"/>
+    </row>
+    <row r="20" spans="1:5" ht="16.5">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+    </row>
+    <row r="21" spans="1:5" ht="16.5">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" spans="1:5" ht="16.5">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+    </row>
+    <row r="23" spans="1:5" ht="16.5">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+    </row>
+    <row r="24" spans="1:5" ht="16.5">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+    </row>
+    <row r="25" spans="1:5" ht="16.5">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+    </row>
+    <row r="26" spans="1:5" ht="16.5">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+    </row>
+    <row r="27" spans="1:5" ht="16.5">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+    </row>
+    <row r="28" spans="1:5" ht="16.5">
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+    </row>
+    <row r="29" spans="1:5" ht="16.5">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+    </row>
+    <row r="30" spans="1:5" ht="16.5">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+    </row>
+    <row r="31" spans="1:5" ht="16.5">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+    </row>
+    <row r="32" spans="1:5" ht="16.5">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+    </row>
+    <row r="33" spans="1:5" ht="16.5">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B19:E19"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.34" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDD54551-29D1-C248-BCC3-669AAD78D534}">
   <sheetPr codeName="Sheet33">
     <tabColor rgb="FFD3C800"/>
@@ -9877,12 +10120,12 @@
     </row>
     <row r="32" spans="1:5" ht="16.5">
       <c r="A32" s="5"/>
-      <c r="B32" s="25" t="s">
+      <c r="B32" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="27"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9892,7 +10135,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5622BACE-1212-6445-8A30-E1A04DAA8C98}">
   <sheetPr codeName="Sheet38">
     <tabColor theme="2" tint="-0.749992370372631"/>
@@ -10208,12 +10451,12 @@
     </row>
     <row r="32" spans="1:5" ht="16.5">
       <c r="A32" s="5"/>
-      <c r="B32" s="25" t="s">
+      <c r="B32" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="27"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10223,7 +10466,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FECB2919-8233-4E01-B177-AF5E1DA3FCB4}">
   <sheetPr>
     <tabColor theme="3" tint="0.39997558519241921"/>
@@ -10539,12 +10782,12 @@
     </row>
     <row r="32" spans="1:5" ht="16.5">
       <c r="A32" s="5"/>
-      <c r="B32" s="25" t="s">
+      <c r="B32" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="27"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10554,7 +10797,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet26">
     <tabColor theme="0" tint="-0.249977111117893"/>
@@ -10703,155 +10946,155 @@
       <c r="E9" s="3"/>
     </row>
     <row r="10" spans="1:5" ht="33" customHeight="1">
-      <c r="A10" s="34">
+      <c r="A10" s="22">
         <v>10</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="35"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="23"/>
     </row>
     <row r="11" spans="1:5" ht="16.5">
-      <c r="A11" s="36"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:5" ht="16.5">
-      <c r="A12" s="36"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
-      <c r="A14" s="36"/>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" spans="1:5" ht="16.5">
-      <c r="A15" s="36"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
     </row>
     <row r="16" spans="1:5" ht="16.5">
-      <c r="A16" s="36"/>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
     </row>
     <row r="17" spans="1:5" ht="16.5">
-      <c r="A17" s="36"/>
-      <c r="B17" s="36"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:5" ht="16.5">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:5" ht="16.5">
-      <c r="A19" s="36"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" ht="16.5">
-      <c r="A20" s="36"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
     </row>
     <row r="21" spans="1:5" ht="16.5">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:5" ht="16.5">
-      <c r="A22" s="36"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
     </row>
     <row r="23" spans="1:5" ht="16.5">
-      <c r="A23" s="36"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
     </row>
     <row r="24" spans="1:5" ht="16.5">
-      <c r="A24" s="36"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" ht="16.5">
-      <c r="A25" s="36"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" spans="1:5" ht="16.5">
-      <c r="A26" s="36"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:5" ht="16.5">
-      <c r="A27" s="36"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
     </row>
     <row r="28" spans="1:5" ht="16.5">
-      <c r="A28" s="36"/>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
     </row>
     <row r="29" spans="1:5" ht="16.5">
-      <c r="A29" s="36"/>
-      <c r="B29" s="36"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="36"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
     </row>
     <row r="30" spans="1:5" ht="16.5">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="1.44" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10859,7 +11102,222 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D918CC59-206B-4E6F-B4B9-D188C671F6A6}">
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="16.5">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="4">
+        <v>30</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" ht="16.5">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="4">
+        <v>30</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" ht="16.5">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="4">
+        <v>3.75</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" ht="16.5">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="4">
+        <v>37.5</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" ht="16.5">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" ht="16.5">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" ht="16.5">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" ht="16.5">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" ht="16.5">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" ht="16.5">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" ht="16.5">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" ht="16.5">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" ht="16.5">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" ht="16.5">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" ht="16.5">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" ht="16.5">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" ht="16.5">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" ht="16.5">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" ht="16.5">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:5" ht="16.5">
+      <c r="A22" s="5"/>
+      <c r="B22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B22:E22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="256" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:E22"/>
@@ -11031,12 +11489,12 @@
     </row>
     <row r="22" spans="1:5" ht="16.5">
       <c r="A22" s="5"/>
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="27"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -11047,7 +11505,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79EE76D-5733-3243-8B4C-150C94FDB466}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:E22"/>
@@ -11219,12 +11677,12 @@
     </row>
     <row r="22" spans="1:5" ht="16.5">
       <c r="A22" s="5"/>
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="27"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -11409,12 +11867,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="9"/>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="30"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="10"/>
@@ -11673,12 +12131,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="27"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="4"/>
@@ -11950,12 +12408,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="27"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="14"/>
@@ -12220,12 +12678,12 @@
     </row>
     <row r="13" spans="1:5" ht="24" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="27"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
@@ -12490,12 +12948,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="27"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>

--- a/مرجع-الطبخات.xlsx
+++ b/مرجع-الطبخات.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6694CCEE-B145-4223-9193-2EDE68CECCAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A429C9B-BCA1-4D38-8137-C4DE0E35DA90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="656" firstSheet="36" activeTab="36" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="656" firstSheet="12" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="لودلين سادة أول" sheetId="9" r:id="rId1"/>
@@ -26,40 +26,41 @@
     <sheet name="لودلين فريز ثاني" sheetId="25" r:id="rId11"/>
     <sheet name="لودلين فريز ثالث" sheetId="30" r:id="rId12"/>
     <sheet name="لودلين فريز رابع" sheetId="35" r:id="rId13"/>
-    <sheet name="لودلين ليمون أول" sheetId="16" r:id="rId14"/>
-    <sheet name="لودلين ليمون ثاني " sheetId="26" r:id="rId15"/>
-    <sheet name="لودلين ليمون ثالث " sheetId="31" r:id="rId16"/>
-    <sheet name="لودلين ليمون رابع" sheetId="36" r:id="rId17"/>
-    <sheet name="لودلين تفاح أول" sheetId="17" r:id="rId18"/>
-    <sheet name="لودلين تفاح ثاني" sheetId="27" r:id="rId19"/>
-    <sheet name="لودلين تفاح ثالث" sheetId="32" r:id="rId20"/>
-    <sheet name="لودلين تفاح رابع" sheetId="37" r:id="rId21"/>
-    <sheet name="معطر ارضيات موف او ليلك" sheetId="13" r:id="rId22"/>
-    <sheet name="معطر ارضيات أبيض - ازهار النرجس" sheetId="38" r:id="rId23"/>
-    <sheet name="معطر ارضيات ازرق - نسيم المحيط " sheetId="39" r:id="rId24"/>
-    <sheet name="معطر ارضيات زهرة التوليب" sheetId="40" r:id="rId25"/>
-    <sheet name="معطر ارضيات رائحة الجوري" sheetId="41" r:id="rId26"/>
-    <sheet name="معطر ارضيات الليمون المنعش" sheetId="42" r:id="rId27"/>
-    <sheet name="معطر ارضيات ببوري" sheetId="43" r:id="rId28"/>
-    <sheet name="عملاق 200 كغ" sheetId="8" r:id="rId29"/>
-    <sheet name="ملمع دواليب" sheetId="6" r:id="rId30"/>
-    <sheet name="ملمع زجاج 150كغ" sheetId="46" r:id="rId31"/>
-    <sheet name="ملمع زجاج 750 كغ" sheetId="5" r:id="rId32"/>
-    <sheet name="ملمع زجاج 1000 كغ" sheetId="47" r:id="rId33"/>
-    <sheet name="طبخة قاشط" sheetId="4" r:id="rId34"/>
-    <sheet name="دوا غسيل بودرا 60 كغ -عطر ببوري" sheetId="49" r:id="rId35"/>
-    <sheet name="دوا غسيل بودرا 157 كغ - ببوري" sheetId="50" r:id="rId36"/>
-    <sheet name="دوا غسيل بودرا - اندومي 100 كغ" sheetId="55" r:id="rId37"/>
-    <sheet name="دوا غسيل بودرا 45كغ مصنع" sheetId="52" r:id="rId38"/>
-    <sheet name="طبخة دوا غسيل بودرا" sheetId="3" r:id="rId39"/>
-    <sheet name="طبخة الشامبو" sheetId="1" r:id="rId40"/>
-    <sheet name="صابون سائل ماء الذهب" sheetId="44" r:id="rId41"/>
-    <sheet name="صابون سائل عود" sheetId="45" r:id="rId42"/>
-    <sheet name="صابون سائل رمان - لافندر" sheetId="51" r:id="rId43"/>
-    <sheet name="صابون سادة" sheetId="2" r:id="rId44"/>
-    <sheet name="طبخة ابو رفيق مغاسل 1.5 طون" sheetId="53" r:id="rId45"/>
-    <sheet name="جدول فارغ غير قابل للتعديل" sheetId="10" r:id="rId46"/>
-    <sheet name="طبخة جديدة 2 (3)" sheetId="14" r:id="rId47"/>
+    <sheet name="لودلين ليمون - 15% ريفا" sheetId="56" r:id="rId14"/>
+    <sheet name="لودلين ليمون أول" sheetId="16" r:id="rId15"/>
+    <sheet name="لودلين ليمون ثاني " sheetId="26" r:id="rId16"/>
+    <sheet name="لودلين ليمون ثالث " sheetId="31" r:id="rId17"/>
+    <sheet name="لودلين ليمون رابع" sheetId="36" r:id="rId18"/>
+    <sheet name="لودلين تفاح أول" sheetId="17" r:id="rId19"/>
+    <sheet name="لودلين تفاح ثاني" sheetId="27" r:id="rId20"/>
+    <sheet name="لودلين تفاح ثالث" sheetId="32" r:id="rId21"/>
+    <sheet name="لودلين تفاح رابع" sheetId="37" r:id="rId22"/>
+    <sheet name="معطر ارضيات موف او ليلك" sheetId="13" r:id="rId23"/>
+    <sheet name="معطر ارضيات أبيض - ازهار النرجس" sheetId="38" r:id="rId24"/>
+    <sheet name="معطر ارضيات ازرق - نسيم المحيط " sheetId="39" r:id="rId25"/>
+    <sheet name="معطر ارضيات زهرة التوليب" sheetId="40" r:id="rId26"/>
+    <sheet name="معطر ارضيات رائحة الجوري" sheetId="41" r:id="rId27"/>
+    <sheet name="معطر ارضيات الليمون المنعش" sheetId="42" r:id="rId28"/>
+    <sheet name="معطر ارضيات ببوري" sheetId="43" r:id="rId29"/>
+    <sheet name="عملاق 200 كغ" sheetId="8" r:id="rId30"/>
+    <sheet name="ملمع دواليب" sheetId="6" r:id="rId31"/>
+    <sheet name="ملمع زجاج 150كغ" sheetId="46" r:id="rId32"/>
+    <sheet name="ملمع زجاج 750 كغ" sheetId="5" r:id="rId33"/>
+    <sheet name="ملمع زجاج 1000 كغ" sheetId="47" r:id="rId34"/>
+    <sheet name="طبخة قاشط" sheetId="4" r:id="rId35"/>
+    <sheet name="دوا غسيل بودرا 60 كغ -عطر ببوري" sheetId="49" r:id="rId36"/>
+    <sheet name="دوا غسيل بودرا 157 كغ - ببوري" sheetId="50" r:id="rId37"/>
+    <sheet name="دوا غسيل بودرا - اندومي 100 كغ" sheetId="55" r:id="rId38"/>
+    <sheet name="دوا غسيل بودرا 45كغ مصنع" sheetId="52" r:id="rId39"/>
+    <sheet name="طبخة دوا غسيل بودرا" sheetId="3" r:id="rId40"/>
+    <sheet name="طبخة الشامبو" sheetId="1" r:id="rId41"/>
+    <sheet name="صابون سائل ماء الذهب" sheetId="44" r:id="rId42"/>
+    <sheet name="صابون سائل عود" sheetId="45" r:id="rId43"/>
+    <sheet name="صابون سائل رمان - لافندر" sheetId="51" r:id="rId44"/>
+    <sheet name="صابون سادة" sheetId="2" r:id="rId45"/>
+    <sheet name="طبخة ابو رفيق مغاسل 1.5 طون" sheetId="53" r:id="rId46"/>
+    <sheet name="جدول فارغ غير قابل للتعديل" sheetId="10" r:id="rId47"/>
+    <sheet name="طبخة جديدة 2 (3)" sheetId="14" r:id="rId48"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="96">
   <si>
     <t>رقم</t>
   </si>
@@ -363,6 +364,9 @@
   <si>
     <t>فورمول سم</t>
   </si>
+  <si>
+    <t>عطر ليمون ريفا</t>
+  </si>
 </sst>
 </file>
 
@@ -432,7 +436,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -551,11 +555,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -617,6 +634,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2180,12 +2206,12 @@
     </row>
     <row r="13" spans="1:5" ht="18.75" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -2253,6 +2279,244 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B20B084A-005F-4D5B-AD30-BD06924453C9}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="8">
+        <v>75</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="8"/>
+    </row>
+    <row r="3" spans="1:5" ht="16.5">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="8">
+        <v>85</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="8"/>
+    </row>
+    <row r="4" spans="1:5" ht="16.5">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="8">
+        <v>10</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="8"/>
+    </row>
+    <row r="5" spans="1:5" ht="16.5">
+      <c r="A5" s="8">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="8">
+        <v>5</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:5" ht="16.5">
+      <c r="A6" s="8">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" spans="1:5" ht="16.5">
+      <c r="A7" s="8">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="8">
+        <v>40</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" spans="1:5" ht="16.5">
+      <c r="A8" s="8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="8">
+        <v>10</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" spans="1:5" ht="16.5">
+      <c r="A9" s="8">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="8">
+        <v>771</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" spans="1:5" ht="16.5">
+      <c r="A10" s="8">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" spans="1:5" ht="16.5">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" ht="16.5">
+      <c r="A12" s="5"/>
+      <c r="B12" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
+    </row>
+    <row r="13" spans="1:5" ht="16.5">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" ht="16.5">
+      <c r="A14" s="5"/>
+      <c r="B14" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="26"/>
+    </row>
+    <row r="15" spans="1:5" ht="16.5">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" ht="16.5">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" ht="16.5">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" ht="16.5">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B12:E12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="11" scale="84" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54985E65-1839-AF4D-A1DF-0F4861F470B1}">
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FFFFFF00"/>
@@ -2512,7 +2776,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64BFB5DD-2769-5749-BB4B-EE8D6916B502}">
   <sheetPr codeName="Sheet9">
     <tabColor rgb="FFFFFF00"/>
@@ -2782,7 +3046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E4207F9-555F-5749-BA70-16C0E666C868}">
   <sheetPr codeName="Sheet14">
     <tabColor rgb="FFFFFF00"/>
@@ -2980,12 +3244,12 @@
     </row>
     <row r="13" spans="1:5" ht="21" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -3052,7 +3316,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E1CAE50-2DC1-7A4D-B27A-538E8E5672DB}">
   <sheetPr codeName="Sheet19">
     <tabColor rgb="FFFFFF00"/>
@@ -3249,12 +3513,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="35"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -3323,7 +3587,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{965DC890-4533-2043-BD50-0D1F55F8D2A2}">
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00B050"/>
@@ -3584,272 +3848,6 @@
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="11" scale="94" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{319F2F22-5303-7649-93A6-CF399F18898E}">
-  <sheetPr codeName="Sheet10">
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16.5">
-      <c r="A2" s="7">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="7">
-        <v>60</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="7"/>
-    </row>
-    <row r="3" spans="1:5" ht="16.5">
-      <c r="A3" s="7">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="7">
-        <v>50</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="7"/>
-    </row>
-    <row r="4" spans="1:5" ht="16.5">
-      <c r="A4" s="7">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="7">
-        <v>7.25</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="7"/>
-    </row>
-    <row r="5" spans="1:5" ht="16.5">
-      <c r="A5" s="7">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="7"/>
-    </row>
-    <row r="6" spans="1:5" ht="16.5">
-      <c r="A6" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="7"/>
-    </row>
-    <row r="7" spans="1:5" ht="16.5">
-      <c r="A7" s="7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="7">
-        <v>10</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="7"/>
-    </row>
-    <row r="8" spans="1:5" ht="16.5">
-      <c r="A8" s="7">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-    </row>
-    <row r="9" spans="1:5" ht="16.5">
-      <c r="A9" s="7">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="7">
-        <v>825</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="7"/>
-    </row>
-    <row r="10" spans="1:5" ht="16.5">
-      <c r="A10" s="7">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="7">
-        <v>50</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="16.5">
-      <c r="A11" s="7">
-        <v>10</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="7"/>
-    </row>
-    <row r="12" spans="1:5" ht="17.100000000000001" customHeight="1">
-      <c r="A12" s="7">
-        <v>11</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="7">
-        <v>1</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="7"/>
-    </row>
-    <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
-      <c r="A13" s="5"/>
-      <c r="B13" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
-    </row>
-    <row r="14" spans="1:5" ht="16.5">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" ht="16.5">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" ht="16.5">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" ht="16.5">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5" ht="16.5">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" ht="16.5">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" ht="16.5">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5" ht="16.5">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B13:E13"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -4018,12 +4016,12 @@
     </row>
     <row r="12" spans="1:5" ht="23.25" customHeight="1">
       <c r="A12" s="9"/>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="29"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="32"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="10"/>
@@ -4042,6 +4040,272 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{319F2F22-5303-7649-93A6-CF399F18898E}">
+  <sheetPr codeName="Sheet10">
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="7">
+        <v>60</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3" spans="1:5" ht="16.5">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="7">
+        <v>50</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:5" ht="16.5">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="7">
+        <v>7.25</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" ht="16.5">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:5" ht="16.5">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5" ht="16.5">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="7">
+        <v>10</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" spans="1:5" ht="16.5">
+      <c r="A8" s="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5" ht="16.5">
+      <c r="A9" s="7">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="7">
+        <v>825</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" ht="16.5">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="7">
+        <v>50</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16.5">
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:5" ht="17.100000000000001" customHeight="1">
+      <c r="A12" s="7">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
+      <c r="A13" s="5"/>
+      <c r="B13" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
+    </row>
+    <row r="14" spans="1:5" ht="16.5">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" ht="16.5">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" ht="16.5">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" ht="16.5">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" ht="16.5">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" ht="16.5">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" ht="16.5">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" ht="16.5">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B13:E13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42FA90AE-4232-4F40-AC8F-E4C816CEF722}">
   <sheetPr codeName="Sheet15">
     <tabColor rgb="FF00B050"/>
@@ -4311,7 +4575,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F1E1CE-24C0-CC4A-8512-28510050A255}">
   <sheetPr codeName="Sheet20">
     <tabColor rgb="FF00B050"/>
@@ -4509,12 +4773,12 @@
     </row>
     <row r="13" spans="1:5" ht="27" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -4581,7 +4845,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0840FCF-F967-7F4E-98DD-C47BB314396B}">
   <sheetPr codeName="Sheet21">
     <tabColor theme="7" tint="-0.249977111117893"/>
@@ -4813,7 +5077,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5BD45AC-0490-8E43-A202-1EEDEBEB427E}">
   <sheetPr codeName="Sheet22">
     <tabColor theme="0" tint="-0.249977111117893"/>
@@ -5033,7 +5297,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA04BDD2-58EF-0F40-AF4D-A9533F7A7FA0}">
   <sheetPr codeName="Sheet23">
     <tabColor theme="3" tint="0.59999389629810485"/>
@@ -5148,12 +5412,12 @@
     </row>
     <row r="8" spans="1:5" ht="16.5">
       <c r="A8" s="9"/>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="29"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="32"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="13"/>
@@ -5255,7 +5519,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9338B1C-EE70-684D-AD37-C90FF6CFF6F0}">
   <sheetPr codeName="Sheet24">
     <tabColor theme="9" tint="0.39997558519241921"/>
@@ -5487,7 +5751,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E821B751-9098-7843-8231-753D4353CEA3}">
   <sheetPr codeName="Sheet35">
     <tabColor theme="6" tint="0.39997558519241921"/>
@@ -5722,7 +5986,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7059576-5640-BE4D-B786-34CA9E68DE20}">
   <sheetPr codeName="Sheet36">
     <tabColor rgb="FFDCD700"/>
@@ -5954,7 +6218,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB816A80-D127-3943-B125-6C3783A1C5D9}">
   <sheetPr codeName="Sheet37">
     <tabColor rgb="FFD7640B"/>
@@ -6171,142 +6435,6 @@
     <mergeCell ref="B8:E8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <sheetPr codeName="Sheet31">
-    <tabColor theme="6" tint="-0.499984740745262"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16.5">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="4">
-        <v>20</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:5" ht="16.5">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="1:5" ht="16.5">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="4">
-        <v>4</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="1:5" ht="16.5">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="4">
-        <v>10</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:5" ht="16.5">
-      <c r="A6" s="4">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5" ht="16.5">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" ht="16.5">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5" ht="16.5">
-      <c r="A9" s="5"/>
-      <c r="B9" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B9:E9"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="11" scale="97" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6565,6 +6693,142 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr codeName="Sheet31">
+    <tabColor theme="6" tint="-0.499984740745262"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="4">
+        <v>20</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="16.5">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" ht="16.5">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="4">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" ht="16.5">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="4">
+        <v>10</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" ht="16.5">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" ht="16.5">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" ht="16.5">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" ht="16.5">
+      <c r="A9" s="5"/>
+      <c r="B9" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B9:E9"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" scale="97" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:E22"/>
@@ -6783,7 +7047,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62480BB5-8217-41E8-9074-0A74142218F0}">
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
@@ -7087,7 +7351,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet29">
     <tabColor theme="3" tint="0.59999389629810485"/>
@@ -7391,7 +7655,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64E45E95-A8F2-4E4D-B56F-29581C2A7CFA}">
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
@@ -7695,7 +7959,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:E25"/>
@@ -7927,7 +8191,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CEE9792-4BCE-445B-8DDB-F636E3EDAAD6}">
   <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -8183,7 +8447,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76356BC6-BD04-49C4-A103-921BA4384AF8}">
   <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -8439,7 +8703,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEC35E0-DAF5-4502-B6DD-6FD4EB7D4329}">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -8678,7 +8942,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B495554-5330-4E3B-92F2-BCD610347704}">
   <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -8808,263 +9072,6 @@
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="1:5" ht="16.5">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:5" ht="16.5">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" ht="16.5">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5" ht="16.5">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" ht="16.5">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" ht="16.5">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" ht="16.5">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5" ht="16.5">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" ht="16.5">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" ht="16.5">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5" ht="16.5">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="1:5" ht="16.5">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="1:5" ht="16.5">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="1:5" ht="16.5">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="1:5" ht="16.5">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="1:5" ht="16.5">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B9:E9"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr codeName="Sheet27"/>
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16.5">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="2">
-        <v>100</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:5" ht="16.5">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="2">
-        <v>30</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" ht="16.5">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" ht="16.5">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="2">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="3"/>
-    </row>
-    <row r="6" spans="1:5" ht="16.5">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="2">
-        <v>200</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:5" ht="16.5">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" ht="16.5">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5" ht="16.5">
-      <c r="A9" s="5"/>
-      <c r="B9" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
-    </row>
-    <row r="10" spans="1:5" ht="16.5">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -9442,6 +9449,263 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr codeName="Sheet27"/>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="2">
+        <v>100</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5" ht="16.5">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="2">
+        <v>30</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" ht="16.5">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" ht="16.5">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="2">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5" ht="16.5">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2">
+        <v>200</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:5" ht="16.5">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" ht="16.5">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" ht="16.5">
+      <c r="A9" s="5"/>
+      <c r="B9" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26"/>
+    </row>
+    <row r="10" spans="1:5" ht="16.5">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" ht="16.5">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" ht="16.5">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" ht="16.5">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" ht="16.5">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" ht="16.5">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" ht="16.5">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" ht="16.5">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" ht="16.5">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" ht="16.5">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" ht="16.5">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" ht="16.5">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:5" ht="16.5">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5" ht="16.5">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:5" ht="16.5">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5" ht="16.5">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5" ht="16.5">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B9:E9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet25">
     <tabColor theme="1" tint="0.499984740745262"/>
@@ -9690,12 +9954,12 @@
     </row>
     <row r="19" spans="1:5" s="19" customFormat="1" ht="27.75">
       <c r="A19" s="21"/>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="35"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="38"/>
     </row>
     <row r="20" spans="1:5" ht="16.5">
       <c r="A20" s="10"/>
@@ -9804,7 +10068,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDD54551-29D1-C248-BCC3-669AAD78D534}">
   <sheetPr codeName="Sheet33">
     <tabColor rgb="FFD3C800"/>
@@ -10135,7 +10399,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5622BACE-1212-6445-8A30-E1A04DAA8C98}">
   <sheetPr codeName="Sheet38">
     <tabColor theme="2" tint="-0.749992370372631"/>
@@ -10466,7 +10730,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FECB2919-8233-4E01-B177-AF5E1DA3FCB4}">
   <sheetPr>
     <tabColor theme="3" tint="0.39997558519241921"/>
@@ -10797,7 +11061,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet26">
     <tabColor theme="0" tint="-0.249977111117893"/>
@@ -11102,7 +11366,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D918CC59-206B-4E6F-B4B9-D188C671F6A6}">
   <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -11317,7 +11581,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:E22"/>
@@ -11505,7 +11769,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79EE76D-5733-3243-8B4C-150C94FDB466}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:E22"/>
@@ -11867,12 +12131,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="9"/>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="29"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="32"/>
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="10"/>

--- a/مرجع-الطبخات.xlsx
+++ b/مرجع-الطبخات.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A429C9B-BCA1-4D38-8137-C4DE0E35DA90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="656" firstSheet="12" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="656" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="لودلين سادة أول" sheetId="9" r:id="rId1"/>

--- a/مرجع-الطبخات.xlsx
+++ b/مرجع-الطبخات.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A429C9B-BCA1-4D38-8137-C4DE0E35DA90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6691141D-465D-44FF-973F-33BE30314DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="656" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="656" firstSheet="19" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="لودلين سادة أول" sheetId="9" r:id="rId1"/>
@@ -18,49 +18,51 @@
     <sheet name="لودلين سادة ثاني" sheetId="20" r:id="rId3"/>
     <sheet name="لودلين سادة ثالث " sheetId="28" r:id="rId4"/>
     <sheet name="لودلين سادة رابع" sheetId="33" r:id="rId5"/>
-    <sheet name="لودلين ليلك أول" sheetId="19" r:id="rId6"/>
-    <sheet name="لودلين ليلك ثاني" sheetId="21" r:id="rId7"/>
-    <sheet name="لودلين ليلك ثالث " sheetId="29" r:id="rId8"/>
-    <sheet name="لودلين ليلك رابع" sheetId="34" r:id="rId9"/>
-    <sheet name="لودلين فريز أول" sheetId="18" r:id="rId10"/>
-    <sheet name="لودلين فريز ثاني" sheetId="25" r:id="rId11"/>
-    <sheet name="لودلين فريز ثالث" sheetId="30" r:id="rId12"/>
-    <sheet name="لودلين فريز رابع" sheetId="35" r:id="rId13"/>
-    <sheet name="لودلين ليمون - 15% ريفا" sheetId="56" r:id="rId14"/>
-    <sheet name="لودلين ليمون أول" sheetId="16" r:id="rId15"/>
-    <sheet name="لودلين ليمون ثاني " sheetId="26" r:id="rId16"/>
-    <sheet name="لودلين ليمون ثالث " sheetId="31" r:id="rId17"/>
-    <sheet name="لودلين ليمون رابع" sheetId="36" r:id="rId18"/>
-    <sheet name="لودلين تفاح أول" sheetId="17" r:id="rId19"/>
-    <sheet name="لودلين تفاح ثاني" sheetId="27" r:id="rId20"/>
-    <sheet name="لودلين تفاح ثالث" sheetId="32" r:id="rId21"/>
-    <sheet name="لودلين تفاح رابع" sheetId="37" r:id="rId22"/>
-    <sheet name="معطر ارضيات موف او ليلك" sheetId="13" r:id="rId23"/>
-    <sheet name="معطر ارضيات أبيض - ازهار النرجس" sheetId="38" r:id="rId24"/>
-    <sheet name="معطر ارضيات ازرق - نسيم المحيط " sheetId="39" r:id="rId25"/>
-    <sheet name="معطر ارضيات زهرة التوليب" sheetId="40" r:id="rId26"/>
-    <sheet name="معطر ارضيات رائحة الجوري" sheetId="41" r:id="rId27"/>
-    <sheet name="معطر ارضيات الليمون المنعش" sheetId="42" r:id="rId28"/>
-    <sheet name="معطر ارضيات ببوري" sheetId="43" r:id="rId29"/>
-    <sheet name="عملاق 200 كغ" sheetId="8" r:id="rId30"/>
-    <sheet name="ملمع دواليب" sheetId="6" r:id="rId31"/>
-    <sheet name="ملمع زجاج 150كغ" sheetId="46" r:id="rId32"/>
-    <sheet name="ملمع زجاج 750 كغ" sheetId="5" r:id="rId33"/>
-    <sheet name="ملمع زجاج 1000 كغ" sheetId="47" r:id="rId34"/>
-    <sheet name="طبخة قاشط" sheetId="4" r:id="rId35"/>
-    <sheet name="دوا غسيل بودرا 60 كغ -عطر ببوري" sheetId="49" r:id="rId36"/>
-    <sheet name="دوا غسيل بودرا 157 كغ - ببوري" sheetId="50" r:id="rId37"/>
-    <sheet name="دوا غسيل بودرا - اندومي 100 كغ" sheetId="55" r:id="rId38"/>
-    <sheet name="دوا غسيل بودرا 45كغ مصنع" sheetId="52" r:id="rId39"/>
-    <sheet name="طبخة دوا غسيل بودرا" sheetId="3" r:id="rId40"/>
-    <sheet name="طبخة الشامبو" sheetId="1" r:id="rId41"/>
-    <sheet name="صابون سائل ماء الذهب" sheetId="44" r:id="rId42"/>
-    <sheet name="صابون سائل عود" sheetId="45" r:id="rId43"/>
-    <sheet name="صابون سائل رمان - لافندر" sheetId="51" r:id="rId44"/>
-    <sheet name="صابون سادة" sheetId="2" r:id="rId45"/>
-    <sheet name="طبخة ابو رفيق مغاسل 1.5 طون" sheetId="53" r:id="rId46"/>
-    <sheet name="جدول فارغ غير قابل للتعديل" sheetId="10" r:id="rId47"/>
-    <sheet name="طبخة جديدة 2 (3)" sheetId="14" r:id="rId48"/>
+    <sheet name="لودلين ليك - 15% ريفا " sheetId="57" r:id="rId6"/>
+    <sheet name="لودلين ليلك أول" sheetId="19" r:id="rId7"/>
+    <sheet name="لودلين ليلك ثاني" sheetId="21" r:id="rId8"/>
+    <sheet name="لودلين ليلك ثالث " sheetId="29" r:id="rId9"/>
+    <sheet name="لودلين ليلك رابع" sheetId="34" r:id="rId10"/>
+    <sheet name="لودلين فريز أول" sheetId="18" r:id="rId11"/>
+    <sheet name="لودلين فريز ثاني" sheetId="25" r:id="rId12"/>
+    <sheet name="لودلين فريز ثالث" sheetId="30" r:id="rId13"/>
+    <sheet name="لودلين فريز رابع" sheetId="35" r:id="rId14"/>
+    <sheet name="لودلين ليمون - 15% ريفا" sheetId="56" r:id="rId15"/>
+    <sheet name="لودلين ليمون أول" sheetId="16" r:id="rId16"/>
+    <sheet name="لودلين ليمون ثاني " sheetId="26" r:id="rId17"/>
+    <sheet name="لودلين ليمون ثالث " sheetId="31" r:id="rId18"/>
+    <sheet name="لودلين ليمون رابع" sheetId="36" r:id="rId19"/>
+    <sheet name="لودلين تفاح أول" sheetId="17" r:id="rId20"/>
+    <sheet name="لودلين تفاح ثاني" sheetId="27" r:id="rId21"/>
+    <sheet name="لودلين تفاح ثالث" sheetId="32" r:id="rId22"/>
+    <sheet name="لودلين تفاح رابع" sheetId="37" r:id="rId23"/>
+    <sheet name="طبخة رابع معدلة 8-8-2026" sheetId="58" r:id="rId24"/>
+    <sheet name="معطر ارضيات موف او ليلك" sheetId="13" r:id="rId25"/>
+    <sheet name="معطر ارضيات أبيض - ازهار النرجس" sheetId="38" r:id="rId26"/>
+    <sheet name="معطر ارضيات ازرق - نسيم المحيط " sheetId="39" r:id="rId27"/>
+    <sheet name="معطر ارضيات زهرة التوليب" sheetId="40" r:id="rId28"/>
+    <sheet name="معطر ارضيات رائحة الجوري" sheetId="41" r:id="rId29"/>
+    <sheet name="معطر ارضيات الليمون المنعش" sheetId="42" r:id="rId30"/>
+    <sheet name="معطر ارضيات ببوري" sheetId="43" r:id="rId31"/>
+    <sheet name="عملاق 200 كغ" sheetId="8" r:id="rId32"/>
+    <sheet name="ملمع دواليب" sheetId="6" r:id="rId33"/>
+    <sheet name="ملمع زجاج 150كغ" sheetId="46" r:id="rId34"/>
+    <sheet name="ملمع زجاج 750 كغ" sheetId="5" r:id="rId35"/>
+    <sheet name="ملمع زجاج 1000 كغ" sheetId="47" r:id="rId36"/>
+    <sheet name="طبخة قاشط" sheetId="4" r:id="rId37"/>
+    <sheet name="دوا غسيل بودرا 60 كغ -عطر ببوري" sheetId="49" r:id="rId38"/>
+    <sheet name="دوا غسيل بودرا 157 كغ - ببوري" sheetId="50" r:id="rId39"/>
+    <sheet name="دوا غسيل بودرا - اندومي 100 كغ" sheetId="55" r:id="rId40"/>
+    <sheet name="دوا غسيل بودرا 45كغ مصنع" sheetId="52" r:id="rId41"/>
+    <sheet name="طبخة دوا غسيل بودرا" sheetId="3" r:id="rId42"/>
+    <sheet name="طبخة الشامبو" sheetId="1" r:id="rId43"/>
+    <sheet name="صابون سائل ماء الذهب" sheetId="44" r:id="rId44"/>
+    <sheet name="صابون سائل عود" sheetId="45" r:id="rId45"/>
+    <sheet name="صابون سائل رمان - لافندر" sheetId="51" r:id="rId46"/>
+    <sheet name="صابون سادة" sheetId="2" r:id="rId47"/>
+    <sheet name="طبخة ابو رفيق مغاسل 1.5 طون" sheetId="53" r:id="rId48"/>
+    <sheet name="جدول فارغ غير قابل للتعديل" sheetId="10" r:id="rId49"/>
+    <sheet name="طبخة جديدة 2 (3)" sheetId="14" r:id="rId50"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -78,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="98">
   <si>
     <t>رقم</t>
   </si>
@@ -367,6 +369,12 @@
   <si>
     <t>عطر ليمون ريفا</t>
   </si>
+  <si>
+    <t>عطر ليلك ريفا</t>
+  </si>
+  <si>
+    <t>طبخة معدلة رابع</t>
+  </si>
 </sst>
 </file>
 
@@ -629,11 +637,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -643,6 +646,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1129,12 +1137,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="4"/>
@@ -1208,6 +1216,276 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54F26A96-1CA6-794D-8D75-AC365217F3BE}">
+  <sheetPr codeName="Sheet17">
+    <tabColor rgb="FF7030A0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="37" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="7">
+        <v>20</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3" spans="1:5" ht="16.5">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="7">
+        <v>40</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:5" ht="16.5">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" ht="16.5">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="7">
+        <v>3</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:5" ht="16.5">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5" ht="16.5">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="7">
+        <v>15</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" spans="1:5" ht="16.5">
+      <c r="A8" s="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5" ht="16.5">
+      <c r="A9" s="7">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="7">
+        <v>890</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" ht="16.5">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="7">
+        <v>100</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16.5">
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:5" ht="17.100000000000001" customHeight="1">
+      <c r="A12" s="7">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
+      <c r="A13" s="5"/>
+      <c r="B13" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
+    </row>
+    <row r="14" spans="1:5" ht="16.5">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" ht="16.5">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" ht="16.5">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" ht="16.5">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" ht="16.5">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" ht="16.5">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" ht="16.5">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" ht="16.5">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B13:E13"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" scale="94" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F11D8E79-8E78-B045-ADEB-346DCF353950}">
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FFFF0000"/>
@@ -1393,12 +1671,12 @@
     </row>
     <row r="12" spans="1:6" ht="21" customHeight="1">
       <c r="A12" s="5"/>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
     </row>
     <row r="13" spans="1:6" ht="16.5">
       <c r="A13" s="4"/>
@@ -1472,7 +1750,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C66E2FD-F596-AA49-AE24-C55163AE00E3}">
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FFFF0000"/>
@@ -1667,12 +1945,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
@@ -1738,7 +2016,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BD8B69A-EB48-DB41-9328-BDA6C4242624}">
   <sheetPr codeName="Sheet13">
     <tabColor rgb="FFFF0000"/>
@@ -1936,12 +2214,12 @@
     </row>
     <row r="13" spans="1:5" ht="21" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
@@ -2008,7 +2286,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4FA1B06-0C43-C145-ADFB-766290F27156}">
   <sheetPr codeName="Sheet18">
     <tabColor rgb="FFFF0000"/>
@@ -2278,7 +2556,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B20B084A-005F-4D5B-AD30-BD06924453C9}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
@@ -2455,12 +2733,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="29"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="4"/>
@@ -2471,12 +2749,12 @@
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="5"/>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="26"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="29"/>
     </row>
     <row r="15" spans="1:5" ht="16.5">
       <c r="A15" s="4"/>
@@ -2516,7 +2794,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54985E65-1839-AF4D-A1DF-0F4861F470B1}">
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FFFFFF00"/>
@@ -2698,12 +2976,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="4"/>
@@ -2776,7 +3054,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64BFB5DD-2769-5749-BB4B-EE8D6916B502}">
   <sheetPr codeName="Sheet9">
     <tabColor rgb="FFFFFF00"/>
@@ -2974,12 +3252,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="14"/>
@@ -3046,7 +3324,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E4207F9-555F-5749-BA70-16C0E666C868}">
   <sheetPr codeName="Sheet14">
     <tabColor rgb="FFFFFF00"/>
@@ -3316,7 +3594,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E1CAE50-2DC1-7A4D-B27A-538E8E5672DB}">
   <sheetPr codeName="Sheet19">
     <tabColor rgb="FFFFFF00"/>
@@ -3584,270 +3862,6 @@
     <mergeCell ref="B13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{965DC890-4533-2043-BD50-0D1F55F8D2A2}">
-  <sheetPr codeName="Sheet5">
-    <tabColor rgb="FF00B050"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="50.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16.5">
-      <c r="A2" s="7">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="7">
-        <v>150</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="7"/>
-    </row>
-    <row r="3" spans="1:5" ht="16.5">
-      <c r="A3" s="7">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="7">
-        <v>100</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="7"/>
-    </row>
-    <row r="4" spans="1:5" ht="16.5">
-      <c r="A4" s="7">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="7">
-        <v>19</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="7"/>
-    </row>
-    <row r="5" spans="1:5" ht="16.5">
-      <c r="A5" s="7">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="7">
-        <v>5</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="7"/>
-    </row>
-    <row r="6" spans="1:5" ht="16.5">
-      <c r="A6" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="7"/>
-    </row>
-    <row r="7" spans="1:5" ht="16.5">
-      <c r="A7" s="7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="7">
-        <v>50</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="7"/>
-    </row>
-    <row r="8" spans="1:5" ht="16.5">
-      <c r="A8" s="7">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-    </row>
-    <row r="9" spans="1:5" ht="16.5">
-      <c r="A9" s="7">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="7">
-        <v>675</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="7"/>
-    </row>
-    <row r="10" spans="1:5" ht="16.5">
-      <c r="A10" s="7">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="7">
-        <v>2</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="16.5">
-      <c r="A11" s="7">
-        <v>10</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="7">
-        <v>25</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="23.25" customHeight="1">
-      <c r="A12" s="5"/>
-      <c r="B12" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
-    </row>
-    <row r="13" spans="1:5" ht="16.5">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5" ht="16.5">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" ht="16.5">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" ht="16.5">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" ht="16.5">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5" ht="16.5">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" ht="16.5">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" ht="16.5">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5" ht="16.5">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B12:E12"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="11" scale="94" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4040,6 +4054,270 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{965DC890-4533-2043-BD50-0D1F55F8D2A2}">
+  <sheetPr codeName="Sheet5">
+    <tabColor rgb="FF00B050"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="50.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="7">
+        <v>150</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3" spans="1:5" ht="16.5">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="7">
+        <v>100</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:5" ht="16.5">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="7">
+        <v>19</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" ht="16.5">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="7">
+        <v>5</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:5" ht="16.5">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5" ht="16.5">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="7">
+        <v>50</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" spans="1:5" ht="16.5">
+      <c r="A8" s="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5" ht="16.5">
+      <c r="A9" s="7">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="7">
+        <v>675</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" ht="16.5">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="7">
+        <v>2</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16.5">
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="7">
+        <v>25</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="23.25" customHeight="1">
+      <c r="A12" s="5"/>
+      <c r="B12" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
+    </row>
+    <row r="13" spans="1:5" ht="16.5">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" ht="16.5">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" ht="16.5">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" ht="16.5">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" ht="16.5">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" ht="16.5">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" ht="16.5">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" ht="16.5">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" ht="16.5">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B12:E12"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" scale="94" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{319F2F22-5303-7649-93A6-CF399F18898E}">
   <sheetPr codeName="Sheet10">
     <tabColor rgb="FF00B050"/>
@@ -4234,12 +4512,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
@@ -4305,7 +4583,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42FA90AE-4232-4F40-AC8F-E4C816CEF722}">
   <sheetPr codeName="Sheet15">
     <tabColor rgb="FF00B050"/>
@@ -4503,12 +4781,12 @@
     </row>
     <row r="13" spans="1:5" ht="23.25" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
@@ -4575,7 +4853,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F1E1CE-24C0-CC4A-8512-28510050A255}">
   <sheetPr codeName="Sheet20">
     <tabColor rgb="FF00B050"/>
@@ -4845,7 +5123,262 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BEFC182-0E6A-4557-BFCC-8893E1A25419}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="37" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="7">
+        <v>10</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3" spans="1:5" ht="16.5">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="7">
+        <v>40</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:5" ht="16.5">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1.25</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" ht="16.5">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="7">
+        <v>3</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:5" ht="16.5">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5" ht="16.5">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="7">
+        <v>15</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" spans="1:5" ht="16.5">
+      <c r="A8" s="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="7">
+        <v>10</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5" ht="16.5">
+      <c r="A9" s="7">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="7">
+        <v>818</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" ht="16.5">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="7">
+        <v>100</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16.5">
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:5" ht="17.100000000000001" customHeight="1">
+      <c r="A12" s="7">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="27" customHeight="1">
+      <c r="A13" s="9"/>
+      <c r="B13" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32"/>
+    </row>
+    <row r="14" spans="1:5" ht="16.5">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+    </row>
+    <row r="15" spans="1:5" ht="16.5">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+    </row>
+    <row r="16" spans="1:5" ht="16.5">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+    </row>
+    <row r="17" spans="1:5" ht="16.5">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+    </row>
+    <row r="18" spans="1:5" ht="16.5">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B13:E13"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" scale="94" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0840FCF-F967-7F4E-98DD-C47BB314396B}">
   <sheetPr codeName="Sheet21">
     <tabColor theme="7" tint="-0.249977111117893"/>
@@ -4970,12 +5503,12 @@
     </row>
     <row r="8" spans="1:5" ht="27.75" customHeight="1">
       <c r="A8" s="5"/>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -5077,7 +5610,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5BD45AC-0490-8E43-A202-1EEDEBEB427E}">
   <sheetPr codeName="Sheet22">
     <tabColor theme="0" tint="-0.249977111117893"/>
@@ -5191,12 +5724,12 @@
     </row>
     <row r="8" spans="1:5" ht="16.5">
       <c r="A8" s="5"/>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -5297,7 +5830,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA04BDD2-58EF-0F40-AF4D-A9533F7A7FA0}">
   <sheetPr codeName="Sheet23">
     <tabColor theme="3" tint="0.59999389629810485"/>
@@ -5519,7 +6052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9338B1C-EE70-684D-AD37-C90FF6CFF6F0}">
   <sheetPr codeName="Sheet24">
     <tabColor theme="9" tint="0.39997558519241921"/>
@@ -5644,12 +6177,12 @@
     </row>
     <row r="8" spans="1:5" ht="32.25" customHeight="1">
       <c r="A8" s="5"/>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -5751,7 +6284,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E821B751-9098-7843-8231-753D4353CEA3}">
   <sheetPr codeName="Sheet35">
     <tabColor theme="6" tint="0.39997558519241921"/>
@@ -5876,12 +6409,12 @@
     </row>
     <row r="8" spans="1:5" ht="30" customHeight="1">
       <c r="A8" s="5"/>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -5983,458 +6516,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.23622047244094491" bottom="0.23622047244094491" header="0.23622047244094491" footer="0.23622047244094491"/>
   <pageSetup paperSize="11" scale="92" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7059576-5640-BE4D-B786-34CA9E68DE20}">
-  <sheetPr codeName="Sheet36">
-    <tabColor rgb="FFDCD700"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="38.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16.5">
-      <c r="A2" s="8">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="8">
-        <v>5</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="8"/>
-    </row>
-    <row r="3" spans="1:5" ht="16.5">
-      <c r="A3" s="8">
-        <v>2</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="8">
-        <v>300</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="8"/>
-    </row>
-    <row r="4" spans="1:5" ht="16.5">
-      <c r="A4" s="8">
-        <v>3</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-    </row>
-    <row r="5" spans="1:5" ht="16.5">
-      <c r="A5" s="8">
-        <v>4</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="8">
-        <v>975</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="8"/>
-    </row>
-    <row r="6" spans="1:5" ht="19.5" customHeight="1">
-      <c r="A6" s="8">
-        <v>5</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="8">
-        <v>10</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="21" customHeight="1">
-      <c r="A7" s="8">
-        <v>6</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="8">
-        <v>10</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A8" s="5"/>
-      <c r="B8" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
-    </row>
-    <row r="9" spans="1:5" ht="16.5">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-    </row>
-    <row r="10" spans="1:5" ht="16.5">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-    </row>
-    <row r="11" spans="1:5" ht="16.5">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-    </row>
-    <row r="12" spans="1:5" ht="16.5">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-    </row>
-    <row r="13" spans="1:5" ht="16.5">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-    </row>
-    <row r="14" spans="1:5" ht="16.5">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-    </row>
-    <row r="15" spans="1:5" ht="16.5">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-    </row>
-    <row r="16" spans="1:5" ht="16.5">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-    </row>
-    <row r="17" spans="1:5" ht="16.5">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-    </row>
-    <row r="18" spans="1:5" ht="16.5">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-    </row>
-    <row r="19" spans="1:5" ht="16.5">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-    </row>
-    <row r="20" spans="1:5" ht="16.5">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-    </row>
-    <row r="21" spans="1:5" ht="16.5">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B8:E8"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="11" scale="87" orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB816A80-D127-3943-B125-6C3783A1C5D9}">
-  <sheetPr codeName="Sheet37">
-    <tabColor rgb="FFD7640B"/>
-  </sheetPr>
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16.5">
-      <c r="A2" s="8">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="8">
-        <v>5</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="8"/>
-    </row>
-    <row r="3" spans="1:5" ht="16.5">
-      <c r="A3" s="8">
-        <v>2</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="8">
-        <v>300</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="8"/>
-    </row>
-    <row r="4" spans="1:5" ht="16.5">
-      <c r="A4" s="8">
-        <v>3</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-    </row>
-    <row r="5" spans="1:5" ht="16.5">
-      <c r="A5" s="8">
-        <v>4</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="8">
-        <v>975</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="8"/>
-    </row>
-    <row r="6" spans="1:5" ht="16.5">
-      <c r="A6" s="8">
-        <v>5</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="8">
-        <v>20</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="16.5">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-    </row>
-    <row r="8" spans="1:5" ht="16.5">
-      <c r="A8" s="5"/>
-      <c r="B8" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
-    </row>
-    <row r="9" spans="1:5" ht="16.5">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-    </row>
-    <row r="10" spans="1:5" ht="16.5">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-    </row>
-    <row r="11" spans="1:5" ht="16.5">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-    </row>
-    <row r="12" spans="1:5" ht="16.5">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-    </row>
-    <row r="13" spans="1:5" ht="16.5">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-    </row>
-    <row r="14" spans="1:5" ht="16.5">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-    </row>
-    <row r="15" spans="1:5" ht="16.5">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-    </row>
-    <row r="16" spans="1:5" ht="16.5">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-    </row>
-    <row r="17" spans="1:5" ht="16.5">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-    </row>
-    <row r="18" spans="1:5" ht="16.5">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-    </row>
-    <row r="19" spans="1:5" ht="16.5">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-    </row>
-    <row r="20" spans="1:5" ht="16.5">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-    </row>
-    <row r="21" spans="1:5" ht="16.5">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B8:E8"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -6613,12 +6694,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="14"/>
@@ -6693,6 +6774,458 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7059576-5640-BE4D-B786-34CA9E68DE20}">
+  <sheetPr codeName="Sheet36">
+    <tabColor rgb="FFDCD700"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="38.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="8">
+        <v>5</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="8"/>
+    </row>
+    <row r="3" spans="1:5" ht="16.5">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="8">
+        <v>300</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="8"/>
+    </row>
+    <row r="4" spans="1:5" ht="16.5">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+    </row>
+    <row r="5" spans="1:5" ht="16.5">
+      <c r="A5" s="8">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="8">
+        <v>975</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:5" ht="19.5" customHeight="1">
+      <c r="A6" s="8">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="8">
+        <v>10</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="21" customHeight="1">
+      <c r="A7" s="8">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="8">
+        <v>10</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="31.5" customHeight="1">
+      <c r="A8" s="5"/>
+      <c r="B8" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
+    </row>
+    <row r="9" spans="1:5" ht="16.5">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" spans="1:5" ht="16.5">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" spans="1:5" ht="16.5">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:5" ht="16.5">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+    </row>
+    <row r="13" spans="1:5" ht="16.5">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+    </row>
+    <row r="14" spans="1:5" ht="16.5">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" spans="1:5" ht="16.5">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" spans="1:5" ht="16.5">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" spans="1:5" ht="16.5">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" spans="1:5" ht="16.5">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+    </row>
+    <row r="19" spans="1:5" ht="16.5">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+    </row>
+    <row r="20" spans="1:5" ht="16.5">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+    </row>
+    <row r="21" spans="1:5" ht="16.5">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B8:E8"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" scale="87" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB816A80-D127-3943-B125-6C3783A1C5D9}">
+  <sheetPr codeName="Sheet37">
+    <tabColor rgb="FFD7640B"/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="8">
+        <v>5</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="8"/>
+    </row>
+    <row r="3" spans="1:5" ht="16.5">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="8">
+        <v>300</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="8"/>
+    </row>
+    <row r="4" spans="1:5" ht="16.5">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+    </row>
+    <row r="5" spans="1:5" ht="16.5">
+      <c r="A5" s="8">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="8">
+        <v>975</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:5" ht="16.5">
+      <c r="A6" s="8">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="8">
+        <v>20</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16.5">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" spans="1:5" ht="16.5">
+      <c r="A8" s="5"/>
+      <c r="B8" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
+    </row>
+    <row r="9" spans="1:5" ht="16.5">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" spans="1:5" ht="16.5">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" spans="1:5" ht="16.5">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:5" ht="16.5">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+    </row>
+    <row r="13" spans="1:5" ht="16.5">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+    </row>
+    <row r="14" spans="1:5" ht="16.5">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" spans="1:5" ht="16.5">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" spans="1:5" ht="16.5">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" spans="1:5" ht="16.5">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" spans="1:5" ht="16.5">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+    </row>
+    <row r="19" spans="1:5" ht="16.5">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+    </row>
+    <row r="20" spans="1:5" ht="16.5">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+    </row>
+    <row r="21" spans="1:5" ht="16.5">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B8:E8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet31">
     <tabColor theme="6" tint="-0.499984740745262"/>
@@ -6812,12 +7345,12 @@
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="5"/>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6828,7 +7361,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:E22"/>
@@ -7032,12 +7565,12 @@
     </row>
     <row r="22" spans="1:5" ht="16.5">
       <c r="A22" s="5"/>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="26"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7047,7 +7580,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62480BB5-8217-41E8-9074-0A74142218F0}">
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
@@ -7209,12 +7742,12 @@
     </row>
     <row r="11" spans="1:5" ht="16.5">
       <c r="A11" s="5"/>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="26"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="29"/>
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="4"/>
@@ -7351,7 +7884,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet29">
     <tabColor theme="3" tint="0.59999389629810485"/>
@@ -7513,12 +8046,12 @@
     </row>
     <row r="11" spans="1:5" ht="16.5">
       <c r="A11" s="5"/>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="26"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="29"/>
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="4"/>
@@ -7655,7 +8188,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64E45E95-A8F2-4E4D-B56F-29581C2A7CFA}">
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
@@ -7817,12 +8350,12 @@
     </row>
     <row r="11" spans="1:5" ht="16.5">
       <c r="A11" s="5"/>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="26"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="29"/>
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="4"/>
@@ -7959,7 +8492,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:E25"/>
@@ -8176,12 +8709,12 @@
     </row>
     <row r="25" spans="1:5" ht="16.5">
       <c r="A25" s="5"/>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="26"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8191,7 +8724,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CEE9792-4BCE-445B-8DDB-F636E3EDAAD6}">
   <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -8311,12 +8844,12 @@
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="5"/>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="29"/>
     </row>
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="4"/>
@@ -8447,7 +8980,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76356BC6-BD04-49C4-A103-921BA4384AF8}">
   <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -8567,511 +9100,18 @@
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="5"/>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="29"/>
     </row>
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="1:5" ht="16.5">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:5" ht="16.5">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" ht="16.5">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5" ht="16.5">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" ht="16.5">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" ht="16.5">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" ht="16.5">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5" ht="16.5">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" ht="16.5">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" ht="16.5">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5" ht="16.5">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="1:5" ht="16.5">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="1:5" ht="16.5">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="1:5" ht="16.5">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="1:5" ht="16.5">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="1:5" ht="16.5">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B9:E9"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEC35E0-DAF5-4502-B6DD-6FD4EB7D4329}">
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="20.25" customHeight="1">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="2">
-        <v>60</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:5" ht="20.25" customHeight="1">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="2">
-        <v>35</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" ht="18.75" customHeight="1">
-      <c r="A4" s="2">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="2">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" ht="20.25" customHeight="1">
-      <c r="A5" s="2">
-        <v>5</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="2">
-        <v>200</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="3"/>
-    </row>
-    <row r="6" spans="1:5" ht="16.5">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5" ht="16.5">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" ht="16.5">
-      <c r="A8" s="5"/>
-      <c r="B8" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
-    </row>
-    <row r="9" spans="1:5" ht="16.5">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:5" ht="16.5">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="1:5" ht="16.5">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:5" ht="16.5">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" ht="16.5">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5" ht="16.5">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" ht="16.5">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" ht="16.5">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" ht="16.5">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5" ht="16.5">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" ht="16.5">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" ht="16.5">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5" ht="16.5">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="1:5" ht="16.5">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="1:5" ht="16.5">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="1:5" ht="16.5">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="1:5" ht="16.5">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B8:E8"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B495554-5330-4E3B-92F2-BCD610347704}">
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="20.25" customHeight="1">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="2">
-        <v>45</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:5" ht="20.25" customHeight="1">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="2">
-        <v>18</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" ht="20.25" customHeight="1">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="2">
-        <v>450</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" ht="18.75" customHeight="1">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="2">
-        <v>5</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="3"/>
-    </row>
-    <row r="6" spans="1:5" ht="20.25" customHeight="1">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="2">
-        <v>95</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:5" ht="16.5">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" ht="16.5">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5" ht="16.5">
-      <c r="A9" s="5"/>
-      <c r="B9" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
-    </row>
-    <row r="10" spans="1:5" ht="16.5">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -9370,12 +9410,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="4"/>
@@ -9449,6 +9489,499 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEC35E0-DAF5-4502-B6DD-6FD4EB7D4329}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="20.25" customHeight="1">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="2">
+        <v>60</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5" ht="20.25" customHeight="1">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="2">
+        <v>35</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="2">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" ht="20.25" customHeight="1">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2">
+        <v>200</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5" ht="16.5">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" ht="16.5">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" ht="16.5">
+      <c r="A8" s="5"/>
+      <c r="B8" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
+    </row>
+    <row r="9" spans="1:5" ht="16.5">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" ht="16.5">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" ht="16.5">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" ht="16.5">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" ht="16.5">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" ht="16.5">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" ht="16.5">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" ht="16.5">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" ht="16.5">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" ht="16.5">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" ht="16.5">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" ht="16.5">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" ht="16.5">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:5" ht="16.5">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5" ht="16.5">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:5" ht="16.5">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5" ht="16.5">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B8:E8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B495554-5330-4E3B-92F2-BCD610347704}">
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="20.25" customHeight="1">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="2">
+        <v>45</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5" ht="20.25" customHeight="1">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="2">
+        <v>18</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" ht="20.25" customHeight="1">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="2">
+        <v>450</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="2">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5" ht="20.25" customHeight="1">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2">
+        <v>95</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:5" ht="16.5">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" ht="16.5">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" ht="16.5">
+      <c r="A9" s="5"/>
+      <c r="B9" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="29"/>
+    </row>
+    <row r="10" spans="1:5" ht="16.5">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" ht="16.5">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" ht="16.5">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" ht="16.5">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" ht="16.5">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" ht="16.5">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" ht="16.5">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" ht="16.5">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" ht="16.5">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" ht="16.5">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" ht="16.5">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" ht="16.5">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:5" ht="16.5">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5" ht="16.5">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:5" ht="16.5">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5" ht="16.5">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5" ht="16.5">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B9:E9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:E26"/>
@@ -9569,12 +10102,12 @@
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="5"/>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="29"/>
     </row>
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="4"/>
@@ -9705,7 +10238,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet25">
     <tabColor theme="1" tint="0.499984740745262"/>
@@ -10068,7 +10601,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDD54551-29D1-C248-BCC3-669AAD78D534}">
   <sheetPr codeName="Sheet33">
     <tabColor rgb="FFD3C800"/>
@@ -10384,12 +10917,12 @@
     </row>
     <row r="32" spans="1:5" ht="16.5">
       <c r="A32" s="5"/>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="26"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10399,7 +10932,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5622BACE-1212-6445-8A30-E1A04DAA8C98}">
   <sheetPr codeName="Sheet38">
     <tabColor theme="2" tint="-0.749992370372631"/>
@@ -10715,12 +11248,12 @@
     </row>
     <row r="32" spans="1:5" ht="16.5">
       <c r="A32" s="5"/>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="26"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10730,7 +11263,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FECB2919-8233-4E01-B177-AF5E1DA3FCB4}">
   <sheetPr>
     <tabColor theme="3" tint="0.39997558519241921"/>
@@ -11046,12 +11579,12 @@
     </row>
     <row r="32" spans="1:5" ht="16.5">
       <c r="A32" s="5"/>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="26"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -11061,7 +11594,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet26">
     <tabColor theme="0" tint="-0.249977111117893"/>
@@ -11366,7 +11899,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D918CC59-206B-4E6F-B4B9-D188C671F6A6}">
   <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -11565,12 +12098,12 @@
     </row>
     <row r="22" spans="1:5" ht="16.5">
       <c r="A22" s="5"/>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="26"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -11581,7 +12114,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:E22"/>
@@ -11753,12 +12286,12 @@
     </row>
     <row r="22" spans="1:5" ht="16.5">
       <c r="A22" s="5"/>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="26"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -11766,193 +12299,6 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="256" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79EE76D-5733-3243-8B4C-150C94FDB466}">
-  <sheetPr codeName="Sheet34"/>
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16.5">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:5" ht="16.5">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="1:5" ht="16.5">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="1:5" ht="16.5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:5" ht="16.5">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5" ht="16.5">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" ht="16.5">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5" ht="16.5">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:5" ht="16.5">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="1:5" ht="16.5">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:5" ht="16.5">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" ht="16.5">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5" ht="16.5">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" ht="16.5">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" ht="16.5">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" ht="16.5">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5" ht="16.5">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" ht="16.5">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" ht="16.5">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5" ht="16.5">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="1:5" ht="16.5">
-      <c r="A22" s="5"/>
-      <c r="B22" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="26"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B22:E22"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -12210,7 +12556,432 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79EE76D-5733-3243-8B4C-150C94FDB466}">
+  <sheetPr codeName="Sheet34"/>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="16.5">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" ht="16.5">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" ht="16.5">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" ht="16.5">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" ht="16.5">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" ht="16.5">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" ht="16.5">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" ht="16.5">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" ht="16.5">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" ht="16.5">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" ht="16.5">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" ht="16.5">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" ht="16.5">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" ht="16.5">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" ht="16.5">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" ht="16.5">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" ht="16.5">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" ht="16.5">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" ht="16.5">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:5" ht="16.5">
+      <c r="A22" s="5"/>
+      <c r="B22" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="29"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B22:E22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4A081C-658A-4BC0-A7F3-2484B4B17302}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="8">
+        <v>75</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="8"/>
+    </row>
+    <row r="3" spans="1:5" ht="16.5">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="8">
+        <v>85</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="8"/>
+    </row>
+    <row r="4" spans="1:5" ht="16.5">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="8">
+        <v>10</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="8"/>
+    </row>
+    <row r="5" spans="1:5" ht="16.5">
+      <c r="A5" s="8">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="8">
+        <v>5</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:5" ht="16.5">
+      <c r="A6" s="8">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" spans="1:5" ht="16.5">
+      <c r="A7" s="8">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="8">
+        <v>40</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" spans="1:5" ht="16.5">
+      <c r="A8" s="8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="8">
+        <v>10</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" spans="1:5" ht="16.5">
+      <c r="A9" s="8">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="8">
+        <v>771</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" spans="1:5" ht="16.5">
+      <c r="A10" s="8">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" spans="1:5" ht="16.5">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" ht="16.5">
+      <c r="A12" s="5"/>
+      <c r="B12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
+    </row>
+    <row r="13" spans="1:5" ht="16.5">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" ht="16.5">
+      <c r="A14" s="5"/>
+      <c r="B14" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="29"/>
+    </row>
+    <row r="15" spans="1:5" ht="16.5">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" ht="16.5">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" ht="16.5">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" ht="16.5">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B14:E14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="11" scale="84" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B8C37C8-EA29-594D-A7D4-0BCC43E0E393}">
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF7030A0"/>
@@ -12395,12 +13166,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="4"/>
@@ -12474,7 +13245,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3FDDD5B-4281-7041-BFCA-5FD5F2DE27C9}">
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF7030A0"/>
@@ -12672,12 +13443,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="14"/>
@@ -12744,7 +13515,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37645F84-B36C-C847-A93C-93484727D804}">
   <sheetPr codeName="Sheet12">
     <tabColor rgb="FF7030A0"/>
@@ -12942,282 +13713,12 @@
     </row>
     <row r="13" spans="1:5" ht="24" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
-    </row>
-    <row r="14" spans="1:5" ht="16.5">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" ht="16.5">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" ht="16.5">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" ht="16.5">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5" ht="16.5">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" ht="16.5">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" ht="16.5">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5" ht="16.5">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B13:E13"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="11" scale="94" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54F26A96-1CA6-794D-8D75-AC365217F3BE}">
-  <sheetPr codeName="Sheet17">
-    <tabColor rgb="FF7030A0"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="37" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16.5">
-      <c r="A2" s="7">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="7">
-        <v>20</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="7"/>
-    </row>
-    <row r="3" spans="1:5" ht="16.5">
-      <c r="A3" s="7">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="7">
-        <v>40</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="7"/>
-    </row>
-    <row r="4" spans="1:5" ht="16.5">
-      <c r="A4" s="7">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="7"/>
-    </row>
-    <row r="5" spans="1:5" ht="16.5">
-      <c r="A5" s="7">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="7">
-        <v>3</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="7"/>
-    </row>
-    <row r="6" spans="1:5" ht="16.5">
-      <c r="A6" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="7"/>
-    </row>
-    <row r="7" spans="1:5" ht="16.5">
-      <c r="A7" s="7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="7">
-        <v>15</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="7"/>
-    </row>
-    <row r="8" spans="1:5" ht="16.5">
-      <c r="A8" s="7">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-    </row>
-    <row r="9" spans="1:5" ht="16.5">
-      <c r="A9" s="7">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="7">
-        <v>890</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="7"/>
-    </row>
-    <row r="10" spans="1:5" ht="16.5">
-      <c r="A10" s="7">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="7">
-        <v>100</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="16.5">
-      <c r="A11" s="7">
-        <v>10</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="7"/>
-    </row>
-    <row r="12" spans="1:5" ht="17.100000000000001" customHeight="1">
-      <c r="A12" s="7">
-        <v>11</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="7">
-        <v>1</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
-      <c r="A13" s="5"/>
-      <c r="B13" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>

--- a/مرجع-الطبخات.xlsx
+++ b/مرجع-الطبخات.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6691141D-465D-44FF-973F-33BE30314DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1B20E0-C5BC-4548-BE1D-25A87FC76EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="656" firstSheet="19" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="656" firstSheet="45" activeTab="47" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="لودلين سادة أول" sheetId="9" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="98">
   <si>
     <t>رقم</t>
   </si>
@@ -637,6 +637,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -646,16 +656,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2484,12 +2484,12 @@
     </row>
     <row r="13" spans="1:5" ht="18.75" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -2733,12 +2733,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="32"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="4"/>
@@ -3522,12 +3522,12 @@
     </row>
     <row r="13" spans="1:5" ht="21" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -4030,12 +4030,12 @@
     </row>
     <row r="12" spans="1:5" ht="23.25" customHeight="1">
       <c r="A12" s="9"/>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="32"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="10"/>
@@ -5051,12 +5051,12 @@
     </row>
     <row r="13" spans="1:5" ht="27" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -5327,12 +5327,12 @@
     </row>
     <row r="13" spans="1:5" ht="27" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -5945,12 +5945,12 @@
     </row>
     <row r="8" spans="1:5" ht="16.5">
       <c r="A8" s="9"/>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="32"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="13"/>
@@ -11908,7 +11908,7 @@
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="5" max="5" width="57.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18">
@@ -11929,80 +11929,108 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5">
-      <c r="A2" s="4"/>
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
       <c r="B2" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C2" s="4">
         <v>4.5</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:5" ht="16.5">
-      <c r="A3" s="4"/>
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
       <c r="B3" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="4">
         <v>30</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:5" ht="16.5">
-      <c r="A4" s="4"/>
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="4">
         <v>30</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:5" ht="16.5">
-      <c r="A5" s="4"/>
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
       <c r="B5" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="4">
         <v>3.75</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:5" ht="16.5">
-      <c r="A6" s="4"/>
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="4">
         <v>37.5</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5" ht="16.5">
-      <c r="A7" s="4"/>
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
       <c r="B7" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C7" s="4">
         <v>2.5</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:5" ht="16.5">
-      <c r="A8" s="4"/>
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
       <c r="B8" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C8" s="4">
         <v>2.5</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
@@ -12109,8 +12137,8 @@
   <mergeCells count="1">
     <mergeCell ref="B22:E22"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="256" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+  <pageMargins left="0.75" right="0.65" top="2.44" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="256" orientation="landscape" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -12477,12 +12505,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="9"/>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="32"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="10"/>
@@ -12920,12 +12948,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="32"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="4"/>

--- a/مرجع-الطبخات.xlsx
+++ b/مرجع-الطبخات.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1B20E0-C5BC-4548-BE1D-25A87FC76EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D62097-F363-4B3C-9761-E7D488503F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="656" firstSheet="45" activeTab="47" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="656" firstSheet="47" activeTab="48" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="لودلين سادة أول" sheetId="9" r:id="rId1"/>
@@ -61,8 +61,9 @@
     <sheet name="صابون سائل رمان - لافندر" sheetId="51" r:id="rId46"/>
     <sheet name="صابون سادة" sheetId="2" r:id="rId47"/>
     <sheet name="طبخة ابو رفيق مغاسل 1.5 طون" sheetId="53" r:id="rId48"/>
-    <sheet name="جدول فارغ غير قابل للتعديل" sheetId="10" r:id="rId49"/>
-    <sheet name="طبخة جديدة 2 (3)" sheetId="14" r:id="rId50"/>
+    <sheet name=" سائل غسيل ابو رفيق - 250كغ  " sheetId="59" r:id="rId49"/>
+    <sheet name="جدول فارغ غير قابل للتعديل" sheetId="10" r:id="rId50"/>
+    <sheet name="طبخة جديدة 2 (3)" sheetId="14" r:id="rId51"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -80,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="103">
   <si>
     <t>رقم</t>
   </si>
@@ -375,6 +376,21 @@
   <si>
     <t>طبخة معدلة رابع</t>
   </si>
+  <si>
+    <t xml:space="preserve">قطرونة </t>
+  </si>
+  <si>
+    <t xml:space="preserve">تكسبون </t>
+  </si>
+  <si>
+    <t>مانع رغوة مائي</t>
+  </si>
+  <si>
+    <t>املجين</t>
+  </si>
+  <si>
+    <t>تم وضع 11 كغ + زاد 50 كغ تحتاج الى تعديل</t>
+  </si>
 </sst>
 </file>
 
@@ -637,16 +653,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1137,12 +1153,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="29"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="4"/>
@@ -1413,12 +1429,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
@@ -1671,12 +1687,12 @@
     </row>
     <row r="12" spans="1:6" ht="21" customHeight="1">
       <c r="A12" s="5"/>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="29"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:6" ht="16.5">
       <c r="A13" s="4"/>
@@ -1945,12 +1961,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
@@ -2214,12 +2230,12 @@
     </row>
     <row r="13" spans="1:5" ht="21" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
@@ -2484,12 +2500,12 @@
     </row>
     <row r="13" spans="1:5" ht="18.75" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -2749,12 +2765,12 @@
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="5"/>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="29"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="26"/>
     </row>
     <row r="15" spans="1:5" ht="16.5">
       <c r="A15" s="4"/>
@@ -2976,12 +2992,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="29"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="4"/>
@@ -3252,12 +3268,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="14"/>
@@ -3522,12 +3538,12 @@
     </row>
     <row r="13" spans="1:5" ht="21" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -4030,12 +4046,12 @@
     </row>
     <row r="12" spans="1:5" ht="23.25" customHeight="1">
       <c r="A12" s="9"/>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="10"/>
@@ -4238,12 +4254,12 @@
     </row>
     <row r="12" spans="1:5" ht="23.25" customHeight="1">
       <c r="A12" s="5"/>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="29"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="4"/>
@@ -4512,12 +4528,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
@@ -4781,12 +4797,12 @@
     </row>
     <row r="13" spans="1:5" ht="23.25" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
@@ -5051,12 +5067,12 @@
     </row>
     <row r="13" spans="1:5" ht="27" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -5327,12 +5343,12 @@
     </row>
     <row r="13" spans="1:5" ht="27" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -5503,12 +5519,12 @@
     </row>
     <row r="8" spans="1:5" ht="27.75" customHeight="1">
       <c r="A8" s="5"/>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="29"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -5724,12 +5740,12 @@
     </row>
     <row r="8" spans="1:5" ht="16.5">
       <c r="A8" s="5"/>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="29"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -5945,12 +5961,12 @@
     </row>
     <row r="8" spans="1:5" ht="16.5">
       <c r="A8" s="9"/>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="13"/>
@@ -6177,12 +6193,12 @@
     </row>
     <row r="8" spans="1:5" ht="32.25" customHeight="1">
       <c r="A8" s="5"/>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="29"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -6409,12 +6425,12 @@
     </row>
     <row r="8" spans="1:5" ht="30" customHeight="1">
       <c r="A8" s="5"/>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="29"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -6694,12 +6710,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="29"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="14"/>
@@ -6898,12 +6914,12 @@
     </row>
     <row r="8" spans="1:5" ht="31.5" customHeight="1">
       <c r="A8" s="5"/>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="29"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -7119,12 +7135,12 @@
     </row>
     <row r="8" spans="1:5" ht="16.5">
       <c r="A8" s="5"/>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="29"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -7345,12 +7361,12 @@
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="5"/>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="29"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7565,12 +7581,12 @@
     </row>
     <row r="22" spans="1:5" ht="16.5">
       <c r="A22" s="5"/>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="29"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7742,12 +7758,12 @@
     </row>
     <row r="11" spans="1:5" ht="16.5">
       <c r="A11" s="5"/>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="29"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="4"/>
@@ -8046,12 +8062,12 @@
     </row>
     <row r="11" spans="1:5" ht="16.5">
       <c r="A11" s="5"/>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="29"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="4"/>
@@ -8350,12 +8366,12 @@
     </row>
     <row r="11" spans="1:5" ht="16.5">
       <c r="A11" s="5"/>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="29"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="4"/>
@@ -8709,12 +8725,12 @@
     </row>
     <row r="25" spans="1:5" ht="16.5">
       <c r="A25" s="5"/>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="29"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8844,12 +8860,12 @@
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="5"/>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="29"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26"/>
     </row>
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="4"/>
@@ -9100,12 +9116,12 @@
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="5"/>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="29"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26"/>
     </row>
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="4"/>
@@ -9410,12 +9426,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="29"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="4"/>
@@ -9593,12 +9609,12 @@
     </row>
     <row r="8" spans="1:5" ht="16.5">
       <c r="A8" s="5"/>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="29"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="4"/>
@@ -9847,12 +9863,12 @@
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="5"/>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="29"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26"/>
     </row>
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="4"/>
@@ -10102,12 +10118,12 @@
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="5"/>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="29"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26"/>
     </row>
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="4"/>
@@ -10917,12 +10933,12 @@
     </row>
     <row r="32" spans="1:5" ht="16.5">
       <c r="A32" s="5"/>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="29"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -11248,12 +11264,12 @@
     </row>
     <row r="32" spans="1:5" ht="16.5">
       <c r="A32" s="5"/>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="29"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -11579,12 +11595,12 @@
     </row>
     <row r="32" spans="1:5" ht="16.5">
       <c r="A32" s="5"/>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="29"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -12126,12 +12142,12 @@
     </row>
     <row r="22" spans="1:5" ht="16.5">
       <c r="A22" s="5"/>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="29"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -12143,8 +12159,7 @@
 </file>
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <sheetPr codeName="Sheet32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F8F46B4-9058-44FB-9595-2DA7A55AB709}">
   <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
@@ -12173,73 +12188,155 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:5" ht="16.5">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="4">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:5" ht="16.5">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="4">
+        <v>15</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:5" ht="16.5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="4">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:5" ht="16.5">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4">
+        <v>2</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5" ht="16.5">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="16.5">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="4">
+        <v>200</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5" ht="16.5">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:5" ht="16.5">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:5" ht="16.5">
@@ -12314,12 +12411,12 @@
     </row>
     <row r="22" spans="1:5" ht="16.5">
       <c r="A22" s="5"/>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="29"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -12505,12 +12602,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="9"/>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="10"/>
@@ -12585,6 +12682,194 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <sheetPr codeName="Sheet32"/>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="16.5">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" ht="16.5">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" ht="16.5">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" ht="16.5">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" ht="16.5">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" ht="16.5">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" ht="16.5">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" ht="16.5">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" ht="16.5">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" ht="16.5">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" ht="16.5">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" ht="16.5">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" ht="16.5">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" ht="16.5">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" ht="16.5">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" ht="16.5">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" ht="16.5">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" ht="16.5">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" ht="16.5">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:5" ht="16.5">
+      <c r="A22" s="5"/>
+      <c r="B22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B22:E22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="256" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79EE76D-5733-3243-8B4C-150C94FDB466}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:E22"/>
@@ -12756,12 +13041,12 @@
     </row>
     <row r="22" spans="1:5" ht="16.5">
       <c r="A22" s="5"/>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="29"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -12964,12 +13249,12 @@
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="5"/>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="29"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="26"/>
     </row>
     <row r="15" spans="1:5" ht="16.5">
       <c r="A15" s="4"/>
@@ -13194,12 +13479,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="29"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="4"/>
@@ -13471,12 +13756,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="14"/>
@@ -13741,12 +14026,12 @@
     </row>
     <row r="13" spans="1:5" ht="24" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
